--- a/artfynd/A 52175-2023 artfynd.xlsx
+++ b/artfynd/A 52175-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52175-2023 artfynd.xlsx
+++ b/artfynd/A 52175-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,119 +2801,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>113193707</v>
-      </c>
-      <c r="B21" t="n">
-        <v>96604</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Annerbergstopet, Skiren  , Sm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>570200</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6341937</v>
-      </c>
-      <c r="S21" t="n">
-        <v>25</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Högsby</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Högsby</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Jan Brenander</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Jan Brenander</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52175-2023 artfynd.xlsx
+++ b/artfynd/A 52175-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,119 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113193707</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96604</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Annerbergstopet, Skiren  , Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570200</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6341937</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52175-2023 artfynd.xlsx
+++ b/artfynd/A 52175-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113176762</v>
+        <v>113176722</v>
       </c>
       <c r="B2" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570061</v>
+        <v>570025</v>
       </c>
       <c r="R2" t="n">
-        <v>6341464</v>
+        <v>6341473</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113177448</v>
+        <v>113176762</v>
       </c>
       <c r="B3" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570046</v>
+        <v>570061</v>
       </c>
       <c r="R3" t="n">
-        <v>6341742</v>
+        <v>6341464</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,51 +871,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178813</v>
+        <v>113192784</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>1639</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Horvan, Sm</t>
+          <t>Annerbergstorpet, Skiren  , Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570095</v>
+        <v>570153</v>
       </c>
       <c r="R4" t="n">
-        <v>6341819</v>
+        <v>6341913</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -955,44 +942,50 @@
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113177496</v>
+        <v>113193188</v>
       </c>
       <c r="B5" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,35 +993,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Horvan, Sm</t>
+          <t>Annerbergstorpet, Skiren  , Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570024</v>
+        <v>570094</v>
       </c>
       <c r="R5" t="n">
-        <v>6341746</v>
+        <v>6341555</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1058,14 +1054,19 @@
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,55 +1075,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178805</v>
+        <v>113177448</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569950</v>
+        <v>570046</v>
       </c>
       <c r="R6" t="n">
-        <v>6341870</v>
+        <v>6341742</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1195,55 +1192,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113176492</v>
+        <v>113192652</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västra Horvan, Sm</t>
+          <t>Annerbergstorpet, Skiren  , Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569996</v>
+        <v>570034</v>
       </c>
       <c r="R7" t="n">
-        <v>6341551</v>
+        <v>6341695</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1273,80 +1264,89 @@
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113176722</v>
+        <v>113192730</v>
       </c>
       <c r="B8" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Horvan, Sm</t>
+          <t>Annerbergstorpet, Skiren  , Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570025</v>
+        <v>569952</v>
       </c>
       <c r="R8" t="n">
-        <v>6341473</v>
+        <v>6341921</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1376,29 +1376,40 @@
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1408,12 +1419,7 @@
         <v>113176506</v>
       </c>
       <c r="B9" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,15 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113192713</v>
+        <v>113177713</v>
       </c>
       <c r="B10" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,24 +1542,18 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Annerbergstorpet, Skiren  , Sm</t>
+          <t>Västra Horvan, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569947</v>
+        <v>569950</v>
       </c>
       <c r="R10" t="n">
-        <v>6341860</v>
+        <v>6341870</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1588,83 +1583,70 @@
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113192652</v>
+        <v>113192713</v>
       </c>
       <c r="B11" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1672,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570034</v>
+        <v>569947</v>
       </c>
       <c r="R11" t="n">
-        <v>6341695</v>
+        <v>6341860</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1745,15 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113192676</v>
+        <v>113192765</v>
       </c>
       <c r="B12" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,37 +1738,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Annerbergstorpet, Skiren  , Sm</t>
+          <t>Annerberstorpet, Skiren  , Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569997</v>
+        <v>570153</v>
       </c>
       <c r="R12" t="n">
-        <v>6341743</v>
+        <v>6341913</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1861,54 +1842,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113193188</v>
+        <v>113178813</v>
       </c>
       <c r="B13" t="n">
-        <v>94322</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Annerbergstorpet, Skiren  , Sm</t>
+          <t>Västra Horvan, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570094</v>
+        <v>570095</v>
       </c>
       <c r="R13" t="n">
-        <v>6341555</v>
+        <v>6341819</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1938,55 +1911,39 @@
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113192625</v>
+        <v>113193146</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,35 +1951,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2030,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570054</v>
+        <v>570153</v>
       </c>
       <c r="R14" t="n">
-        <v>6341476</v>
+        <v>6341913</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2084,6 +2032,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2105,12 +2054,7 @@
         <v>113192595</v>
       </c>
       <c r="B15" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,12 +2165,7 @@
         <v>113192614</v>
       </c>
       <c r="B16" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2334,37 +2273,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113192784</v>
+        <v>113192676</v>
       </c>
       <c r="B17" t="n">
-        <v>78707</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1639</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2377,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570153</v>
+        <v>569997</v>
       </c>
       <c r="R17" t="n">
-        <v>6341913</v>
+        <v>6341743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,15 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113192730</v>
+        <v>113176492</v>
       </c>
       <c r="B18" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2466,38 +2395,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Annerbergstorpet, Skiren  , Sm</t>
+          <t>Västra Horvan, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569952</v>
+        <v>569996</v>
       </c>
       <c r="R18" t="n">
-        <v>6341921</v>
+        <v>6341551</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2527,82 +2457,75 @@
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113193146</v>
+        <v>113192625</v>
       </c>
       <c r="B19" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2610,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570153</v>
+        <v>570054</v>
       </c>
       <c r="R19" t="n">
-        <v>6341913</v>
+        <v>6341476</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2587,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2683,57 +2605,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113192765</v>
+        <v>113177496</v>
       </c>
       <c r="B20" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Annerberstorpet, Skiren  , Sm</t>
+          <t>Västra Horvan, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570153</v>
+        <v>570024</v>
       </c>
       <c r="R20" t="n">
-        <v>6341913</v>
+        <v>6341746</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2763,19 +2674,14 @@
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-11-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:30</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,19 +2690,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2806,12 +2711,7 @@
         <v>113193707</v>
       </c>
       <c r="B21" t="n">
-        <v>96604</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 52175-2023 artfynd.xlsx
+++ b/artfynd/A 52175-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113176722</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113176762</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113193188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113177448</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192730</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113176506</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113177713</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192713</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192765</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178813</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113193146</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2159,6 +2229,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192595</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2381,6 +2461,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192676</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2483,6 +2568,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113176492</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2602,6 +2692,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113192625</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113177496</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,8 +2913,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113193707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>